--- a/modeleLogiqueSBM/ig/StructureDefinition-fr-lm-condition.xlsx
+++ b/modeleLogiqueSBM/ig/StructureDefinition-fr-lm-condition.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1067" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1036" uniqueCount="190">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T14:45:49+00:00</t>
+    <t>2026-04-08T10:07:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -406,15 +406,6 @@
   </si>
   <si>
     <t>fr-lm-entry.header.langue</t>
-  </si>
-  <si>
-    <t>fr-lm-condition.header.code</t>
-  </si>
-  <si>
-    <t>Type de l'entrée</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.code</t>
   </si>
   <si>
     <t>fr-lm-condition.type</t>
@@ -919,7 +910,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ33"/>
+  <dimension ref="A1:AJ32"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="42.0859375" customWidth="true" bestFit="true"/>
@@ -2482,7 +2473,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>79</v>
@@ -2533,10 +2524,10 @@
         <v>73</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>73</v>
+        <v>130</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>73</v>
@@ -2554,10 +2545,10 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>79</v>
@@ -2571,10 +2562,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2600,10 +2591,10 @@
         <v>121</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2633,10 +2624,10 @@
         <v>73</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>132</v>
+        <v>73</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>73</v>
@@ -2654,7 +2645,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -2671,10 +2662,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2697,7 +2688,7 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="L18" t="s" s="2">
         <v>135</v>
@@ -2754,7 +2745,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -2766,15 +2757,15 @@
         <v>73</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>73</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2782,7 +2773,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>79</v>
@@ -2797,13 +2788,13 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2854,10 +2845,10 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>79</v>
@@ -2866,26 +2857,26 @@
         <v>73</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>139</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>73</v>
+        <v>143</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>73</v>
@@ -2897,15 +2888,17 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>146</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>73</v>
@@ -2942,50 +2935,50 @@
         <v>73</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>73</v>
+        <v>148</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>73</v>
+        <v>150</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>73</v>
+        <v>136</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>146</v>
+        <v>73</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>73</v>
@@ -2997,16 +2990,16 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3044,39 +3037,39 @@
         <v>73</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>151</v>
+        <v>73</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>152</v>
+        <v>73</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>153</v>
+        <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>139</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3084,7 +3077,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>79</v>
@@ -3099,17 +3092,15 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>159</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>73</v>
@@ -3158,10 +3149,10 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>79</v>
@@ -3170,15 +3161,15 @@
         <v>73</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>73</v>
+        <v>163</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3201,13 +3192,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>162</v>
+        <v>117</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3258,7 +3249,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -3270,15 +3261,15 @@
         <v>73</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>166</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3304,10 +3295,10 @@
         <v>117</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3358,7 +3349,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -3375,10 +3366,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3401,13 +3392,13 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3437,10 +3428,10 @@
         <v>73</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>73</v>
+        <v>170</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>73</v>
+        <v>171</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>73</v>
@@ -3458,7 +3449,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
@@ -3475,10 +3466,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3504,10 +3495,10 @@
         <v>121</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3537,10 +3528,10 @@
         <v>73</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>73</v>
@@ -3558,7 +3549,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -3575,10 +3566,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3604,10 +3595,10 @@
         <v>121</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3637,10 +3628,10 @@
         <v>73</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>177</v>
+        <v>73</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>178</v>
+        <v>73</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>73</v>
@@ -3658,7 +3649,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -3675,10 +3666,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3689,7 +3680,7 @@
         <v>74</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>73</v>
@@ -3704,10 +3695,10 @@
         <v>121</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3758,13 +3749,13 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>73</v>
@@ -3775,10 +3766,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3804,10 +3795,10 @@
         <v>121</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3858,7 +3849,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -3875,10 +3866,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3889,7 +3880,7 @@
         <v>74</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>73</v>
@@ -3904,10 +3895,10 @@
         <v>121</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3937,10 +3928,10 @@
         <v>73</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>73</v>
+        <v>184</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>73</v>
+        <v>185</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>73</v>
@@ -3958,13 +3949,13 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>73</v>
@@ -3975,10 +3966,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -3986,10 +3977,10 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>73</v>
@@ -4001,13 +3992,13 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>121</v>
+        <v>153</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4037,10 +4028,10 @@
         <v>73</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>187</v>
+        <v>73</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>188</v>
+        <v>73</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>73</v>
@@ -4058,13 +4049,13 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>73</v>
@@ -4075,10 +4066,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4086,10 +4077,10 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>73</v>
@@ -4101,13 +4092,13 @@
         <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4158,118 +4149,18 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="C33" s="2"/>
-      <c r="D33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E33" s="2"/>
-      <c r="F33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G33" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K33" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="L33" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
-      <c r="P33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q33" s="2"/>
-      <c r="R33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AG33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH33" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ33" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/modeleLogiqueSBM/ig/StructureDefinition-fr-lm-condition.xlsx
+++ b/modeleLogiqueSBM/ig/StructureDefinition-fr-lm-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T10:07:24+00:00</t>
+    <t>2026-04-08T12:33:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
